--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>1. The menu is not scanned.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>KO</t>
+          <t>The menu is now scanned correctly.</t>
+        </is>
+      </c>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>FIXED</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1nAERQz7NylVKp3-O6VJW9tZcGmua-6H9/view?usp=drive_link</t>
+          <t>Fixed: removed manual Content-Type header from ai.service.ts scanMenu (was breaking multipart/boundary). Increased timeout to 120s to accommodate GPT-4 Vision processing time.</t>
         </is>
       </c>
     </row>
@@ -676,15 +676,19 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>1. The menu is not scanned.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="n"/>
+          <t>The menu is now scanned correctly.</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t>Fixed: removed manual Content-Type header from ai.service.ts scanMenu (was breaking multipart/boundary). Increased timeout to 120s to accommodate GPT-4 Vision processing time.</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="60" customFormat="1" customHeight="1" s="3">
       <c r="A6" s="1" t="n">

--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -634,17 +634,17 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>The menu is now scanned correctly.</t>
-        </is>
-      </c>
-      <c r="G4" s="11" t="inlineStr">
-        <is>
-          <t>FIXED</t>
+          <t>1. The menu is not scanned.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>KO</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>Fixed: removed manual Content-Type header from ai.service.ts scanMenu (was breaking multipart/boundary). Increased timeout to 120s to accommodate GPT-4 Vision processing time.</t>
+          <t>https://drive.google.com/file/d/1nAERQz7NylVKp3-O6VJW9tZcGmua-6H9/view?usp=drive_link</t>
         </is>
       </c>
     </row>
@@ -676,19 +676,15 @@
       </c>
       <c r="F5" s="1" t="inlineStr">
         <is>
-          <t>The menu is now scanned correctly.</t>
-        </is>
-      </c>
-      <c r="G5" s="11" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="inlineStr">
-        <is>
-          <t>Fixed: removed manual Content-Type header from ai.service.ts scanMenu (was breaking multipart/boundary). Increased timeout to 120s to accommodate GPT-4 Vision processing time.</t>
-        </is>
-      </c>
+          <t>1. The menu is not scanned.</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6" ht="60" customFormat="1" customHeight="1" s="3">
       <c r="A6" s="1" t="n">

--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -1,66 +1,228 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F122E6-F105-4640-AD57-AC2DD17C3B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="49">
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Pasos</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Obtained Result</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>CAR001</t>
+  </si>
+  <si>
+    <t>CAR002</t>
+  </si>
+  <si>
+    <t>CAR003</t>
+  </si>
+  <si>
+    <t>CAR004</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1nAERQz7NylVKp3-O6VJW9tZcGmua-6H9/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Escanear Carta con IA"
+2. The user charges an image. 
+3. The user clicks "Escanear Carta"</t>
+  </si>
+  <si>
+    <t>1. The user clicks "Escanear Carta con IA"
+2. The user charges an image. 
+3. The user clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The operation is cancelled.</t>
+  </si>
+  <si>
+    <t>1. An error is shown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Añadir carta"
+2. The user fills the fields in Productos y precios" : Nombre, descripción y selecciona un producto.
+3. The user clicks "Crear"
+</t>
+  </si>
+  <si>
+    <t>1. The menu is not created.</t>
+  </si>
+  <si>
+    <t>1. The menu is created.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user sees the Menus' home
+</t>
+  </si>
+  <si>
+    <t>1. The Menus' home is correctly.</t>
+  </si>
+  <si>
+    <t>1. The menu is scanned.</t>
+  </si>
+  <si>
+    <t>1. The menu is not scanned.</t>
+  </si>
+  <si>
+    <t>Scan menu</t>
+  </si>
+  <si>
+    <t>Error: Scan menu</t>
+  </si>
+  <si>
+    <t>Add menu</t>
+  </si>
+  <si>
+    <t>Menus' home</t>
+  </si>
+  <si>
+    <t>1. A modifier is created</t>
+  </si>
+  <si>
+    <t>1. A modifier is not created</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Modificadores"
+2. The user  fills the fields
+3. The user cliks "Crear"
+</t>
+  </si>
+  <si>
+    <t>CAR005</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/1iQVw2ssQU4ip7j2sEqfApVI-YwxE2qzW/view?usp=drive_link</t>
+  </si>
+  <si>
+    <t>New modifiers</t>
+  </si>
+  <si>
+    <t>Error: New menu, mandatory fields</t>
+  </si>
+  <si>
+    <t>CAR006</t>
+  </si>
+  <si>
+    <t>Error: New modifier, mandatory fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks "Modificadores"
+2. The user does not fill mandatory fields
+3. The user cliks "Crear"
+</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>Bloqueada por CAR005</t>
+  </si>
+  <si>
+    <t>CAR007</t>
+  </si>
+  <si>
+    <t>Select diferents restaurants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user clicks a "Restaurante"
+</t>
+  </si>
+  <si>
+    <t>1. The restaurant is selected and updated.</t>
+  </si>
+  <si>
+    <t>PTE</t>
+  </si>
+  <si>
+    <t>No se muestran restaurantes</t>
+  </si>
+  <si>
+    <t>Al dar a añadir carta no hace nada. Tampoco se ha podido añadir producto, si ese es el motivo u  otro error, falta mensaje de error explicativo.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00276221"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -102,53 +264,50 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="3" tint="0.5999633777886288"/>
+          <bgColor theme="3" tint="0.59996337778862885"/>
         </patternFill>
       </fill>
     </dxf>
@@ -178,7 +337,19 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6565"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -466,416 +637,274 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col width="9.140625" customWidth="1" style="6" min="1" max="1"/>
-    <col width="15" customWidth="1" style="6" min="2" max="2"/>
-    <col width="48" customWidth="1" style="6" min="3" max="3"/>
-    <col width="41.5703125" customWidth="1" style="6" min="4" max="4"/>
-    <col width="33.42578125" customWidth="1" style="6" min="5" max="6"/>
-    <col width="9.140625" customWidth="1" style="6" min="7" max="7"/>
-    <col width="91.42578125" bestFit="1" customWidth="1" style="6" min="8" max="8"/>
-    <col width="9.140625" customWidth="1" style="6" min="9" max="16384"/>
+    <col min="1" max="1" width="9.140625" style="6"/>
+    <col min="2" max="2" width="15" style="6" customWidth="1"/>
+    <col min="3" max="3" width="48" style="6" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" style="6" customWidth="1"/>
+    <col min="5" max="6" width="33.42578125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="6"/>
+    <col min="8" max="8" width="91.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Num</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>ID</t>
-        </is>
-      </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>Summary</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Pasos</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Expected Result</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Obtained Result</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2" ht="30" customFormat="1" customHeight="1" s="3">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>CAR001</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>Menus' home</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user sees the Menus' home
-</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>1. The Menus' home is correctly.</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>1. The Menus' home is correctly.</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="n"/>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="7"/>
     </row>
-    <row r="3" ht="90" customFormat="1" customHeight="1" s="3">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>CAR002</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Add menu</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks "Añadir carta"
-2. The user fills the fields in Productos y precios" : Nombre, descripción y selecciona un producto.
-3. The user clicks "Crear"
-</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>1. The menu is created.</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Al hacer click en Añadir carta se abre el modal. Los errores al guardar se muestran en el modal.</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="inlineStr">
-        <is>
-          <t>FIXED</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>SOLUCIONADO: CartasPage.tsx - el handleSubmit ahora re-lanza el error (throw e) para que el CartaModal lo reciba y muestre el mensaje de error inline encima del footer del modal. Ya no falla silenciosamente.</t>
-        </is>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
-    <row r="4" ht="45" customFormat="1" customHeight="1" s="3">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>CAR003</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>Scan menu</t>
-        </is>
-      </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>1. The user clicks "Escanear Carta con IA"
-2. The user charges an image. 
-3. The user clicks "Escanear Carta"</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>1. The menu is scanned.</t>
-        </is>
-      </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>1. The menu is not scanned.</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1nAERQz7NylVKp3-O6VJW9tZcGmua-6H9/view?usp=drive_link</t>
-        </is>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" ht="45" customFormat="1" customHeight="1" s="3">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>CAR003</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Error: Scan menu</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>1. The user clicks "Escanear Carta con IA"
-2. The user charges an image. 
-3. The user clicks "Cancelar"</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>1. The operation is cancelled.</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>1. The menu is not scanned.</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H5" s="7" t="n"/>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="7"/>
     </row>
-    <row r="6" ht="60" customFormat="1" customHeight="1" s="3">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>CAR004</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>Error: New menu, mandatory fields</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks "Modificadores"
-2. The user does not fill mandatory fields
-3. The user cliks "Crear"
-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="H6" s="1" t="n"/>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="1"/>
     </row>
-    <row r="7" ht="60" customFormat="1" customHeight="1" s="3">
-      <c r="A7" s="1" t="n">
+    <row r="7" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>CAR005</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>New modifiers</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks "Modificadores"
-2. The user  fills the fields
-3. The user cliks "Crear"
-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>1. A modifier is created</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>1. A modifier is not created</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>KO</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>https://drive.google.com/file/d/1iQVw2ssQU4ip7j2sEqfApVI-YwxE2qzW/view?usp=drive_link</t>
-        </is>
+      <c r="B7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="8" ht="60" customFormat="1" customHeight="1" s="3">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>CAR006</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>Error: New modifier, mandatory fields</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks "Modificadores"
-2. The user does not fill mandatory fields
-3. The user cliks "Crear"
-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>1. An error is shown</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>BL</t>
-        </is>
-      </c>
-      <c r="H8" s="1" t="inlineStr">
-        <is>
-          <t>Bloqueada por CAR005</t>
-        </is>
+      <c r="B8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="9" ht="30" customFormat="1" customHeight="1" s="3">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>CAR007</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Select diferents restaurants</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. The user clicks a "Restaurante"
-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>1. The restaurant is selected and updated.</t>
-        </is>
-      </c>
-      <c r="F9" s="1" t="n"/>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>PTE</t>
-        </is>
-      </c>
-      <c r="H9" s="1" t="inlineStr">
-        <is>
-          <t>No se muestran restaurantes</t>
-        </is>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
-    <row r="10">
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G9">
-    <cfRule type="containsText" priority="3" operator="containsText" dxfId="3" text="KO">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" priority="5" operator="containsText" dxfId="2" text="OK">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G8:G9">
-    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" text="BL">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9">
-    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" text="PTE">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G9)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId1"/>
+    <hyperlink ref="H7" r:id="rId1" xr:uid="{7AD228BA-C3ED-49A4-880A-FD0C902A1C92}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCases\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43F122E6-F105-4640-AD57-AC2DD17C3B59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD141751-4470-41F4-9237-940346743B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1545" yWindow="750" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
   <si>
     <t>Num</t>
   </si>
@@ -59,9 +59,6 @@
   </si>
   <si>
     <t>OK</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/file/d/1nAERQz7NylVKp3-O6VJW9tZcGmua-6H9/view?usp=drive_link</t>
   </si>
   <si>
     <t>KO</t>
@@ -89,9 +86,6 @@
 </t>
   </si>
   <si>
-    <t>1. The menu is not created.</t>
-  </si>
-  <si>
     <t>1. The menu is created.</t>
   </si>
   <si>
@@ -175,20 +169,118 @@
     <t>1. The restaurant is selected and updated.</t>
   </si>
   <si>
-    <t>PTE</t>
-  </si>
-  <si>
-    <t>No se muestran restaurantes</t>
-  </si>
-  <si>
-    <t>Al dar a añadir carta no hace nada. Tampoco se ha podido añadir producto, si ese es el motivo u  otro error, falta mensaje de error explicativo.</t>
+    <t>CAR008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu and clicks the icon "+"
+</t>
+  </si>
+  <si>
+    <t>1. The menu is published</t>
+  </si>
+  <si>
+    <t>Published menu</t>
+  </si>
+  <si>
+    <t>1. The menu is not published</t>
+  </si>
+  <si>
+    <t>15/04/26 : Error: carta_sca.jpg</t>
+  </si>
+  <si>
+    <t>15/04/26 : An error is shown:carta_pub.jpg</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Al dar a añadir carta no hace nada. Tampoco se ha podido añadir producto, si ese es el motivo u  otro error, falta mensaje de error explicativo.
+15/04/26 : SOLUCIONADO: CartasPage.tsx - el handleSubmit ahora re-lanza el error (throw e) para que el CartaModal lo reciba y muestre el mensaje de error inline encima del footer del modal. Ya no falla silenciosamente.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>15/04/26 : Al crear la carta y guardar, se abre un menú con el botón "Continuar", antes de dar tiempo a pulsar el botón se cierra. Esta ventana/mensaje sobra.
+15/04/26: Error al introducir un valor muy alto en uno de los productos: carta_crear.jpg
+15/06/26: Controlar longitud del nombre: carta_crear_nom.jpg</t>
+    </r>
+  </si>
+  <si>
+    <t>Published menu: QR</t>
+  </si>
+  <si>
+    <t>Published menu: Copy URL</t>
+  </si>
+  <si>
+    <t>Published menu: Close</t>
+  </si>
+  <si>
+    <t>Published menu: Unpublish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu and clicks the icon "+"
+". Scans the QR
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu and clicks the icon "+"
+2. The user copies the URL in a navegator
+</t>
+  </si>
+  <si>
+    <t>1. The url works correctly.</t>
+  </si>
+  <si>
+    <t>1. The published menu is closed</t>
+  </si>
+  <si>
+    <t>1. The QR works correctly.</t>
+  </si>
+  <si>
+    <t>Published menu: Unpublish, cancel</t>
+  </si>
+  <si>
+    <t>CAR009</t>
+  </si>
+  <si>
+    <t>CAR010</t>
+  </si>
+  <si>
+    <t>CAR011</t>
+  </si>
+  <si>
+    <t>CAR012</t>
+  </si>
+  <si>
+    <t>CAR013</t>
+  </si>
+  <si>
+    <t>1. The user selects a menu and clicks the icon "+"
+2. Clicks "Cerrar"</t>
+  </si>
+  <si>
+    <t>1. The user selects a menu and clicks the icon "+"
+2. Clicks "Despublicar"
+3. Clicks "Despublicar"</t>
+  </si>
+  <si>
+    <t>1. The user selects a menu and clicks the icon "+"
+2. Clicks "Despublicar"
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>1. The menu is unpublished</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,6 +304,19 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -295,15 +400,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6565"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -638,7 +774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6"/>
@@ -685,23 +821,23 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" s="3" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="3" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -709,22 +845,20 @@
         <v>9</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="F3" s="1"/>
       <c r="G3" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -735,22 +869,22 @@
         <v>10</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="7" t="s">
         <v>13</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -761,16 +895,16 @@
         <v>10</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F5" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>12</v>
@@ -785,16 +919,16 @@
         <v>11</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>12</v>
@@ -806,25 +940,25 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>35</v>
-      </c>
       <c r="D7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -832,25 +966,25 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="E8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>39</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -858,49 +992,203 @@
         <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="E9" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="F9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="C10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
+      <c r="F10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G9">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="KO">
+  <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="G2 G4:G15">
+    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G9">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="BL">
+  <conditionalFormatting sqref="G8:G15">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="PTE">
+  <conditionalFormatting sqref="G9:G15">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G9)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
+      <formula>NOT(ISERROR(SEARCH("KO",G3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",G3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>

--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD141751-4470-41F4-9237-940346743B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1545" yWindow="750" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -410,6 +410,20 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF006100"/>
       </font>
@@ -437,20 +451,6 @@
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1159,36 +1159,38 @@
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2 G4:G15">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="KO">
+  <conditionalFormatting sqref="G2:G3">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="9" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="PTE">
+      <formula>NOT(ISERROR(SEARCH("PTE",G3)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="BL">
+      <formula>NOT(ISERROR(SEARCH("BL",G3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4:G15">
+    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="KO">
+      <formula>NOT(ISERROR(SEARCH("KO",G4)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="OK">
+      <formula>NOT(ISERROR(SEARCH("OK",G4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G8:G15">
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G8)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G9:G15">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="PTE">
+    <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G9)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
-      <formula>NOT(ISERROR(SEARCH("PTE",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
-      <formula>NOT(ISERROR(SEARCH("BL",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G3)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>

--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD141751-4470-41F4-9237-940346743B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="960" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD141751-4470-41F4-9237-940346743B08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC15573F-AAA4-4B78-8431-42DE32B8969B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="615" windowWidth="27795" windowHeight="14865" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
   <si>
     <t>Num</t>
   </si>
@@ -172,23 +172,13 @@
     <t>CAR008</t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user selects a menu and clicks the icon "+"
-</t>
-  </si>
-  <si>
     <t>1. The menu is published</t>
   </si>
   <si>
     <t>Published menu</t>
   </si>
   <si>
-    <t>1. The menu is not published</t>
-  </si>
-  <si>
     <t>15/04/26 : Error: carta_sca.jpg</t>
-  </si>
-  <si>
-    <t>15/04/26 : An error is shown:carta_pub.jpg</t>
   </si>
   <si>
     <r>
@@ -213,31 +203,9 @@
     <t>Published menu: QR</t>
   </si>
   <si>
-    <t>Published menu: Copy URL</t>
-  </si>
-  <si>
-    <t>Published menu: Close</t>
-  </si>
-  <si>
     <t>Published menu: Unpublish</t>
   </si>
   <si>
-    <t xml:space="preserve">1. The user selects a menu and clicks the icon "+"
-". Scans the QR
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. The user selects a menu and clicks the icon "+"
-2. The user copies the URL in a navegator
-</t>
-  </si>
-  <si>
-    <t>1. The url works correctly.</t>
-  </si>
-  <si>
-    <t>1. The published menu is closed</t>
-  </si>
-  <si>
     <t>1. The QR works correctly.</t>
   </si>
   <si>
@@ -257,10 +225,6 @@
   </si>
   <si>
     <t>CAR013</t>
-  </si>
-  <si>
-    <t>1. The user selects a menu and clicks the icon "+"
-2. Clicks "Cerrar"</t>
   </si>
   <si>
     <t>1. The user selects a menu and clicks the icon "+"
@@ -268,19 +232,122 @@
 3. Clicks "Despublicar"</t>
   </si>
   <si>
+    <t>1. The menu is unpublished</t>
+  </si>
+  <si>
+    <t>Published menu: Copy</t>
+  </si>
+  <si>
+    <t>Published menu: cancel</t>
+  </si>
+  <si>
+    <t>1. The user selects a menu and clicks the icon "+"
+2. The message "Publicar esta carta la hará accesible mediante un enlace público y un código QR que los clientes pueden escanear desde sus dispositivos móviles." is shown
+3. Clicks "Publicar carta"</t>
+  </si>
+  <si>
+    <t>1. The user selects a menu and clicks the icon "+"
+2. The message "Publicar esta carta la hará accesible mediante un enlace público y un código QR que los clientes pueden escanear desde sus dispositivos móviles." is shown
+3. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a published menu
+2.  Scans the QR
+</t>
+  </si>
+  <si>
+    <t>Published menu: URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. QR works correctly.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. URL works correctly.
+</t>
+  </si>
+  <si>
+    <t>La url creada no funciona.</t>
+  </si>
+  <si>
+    <t>15/04/26 : An error is shown:carta_pub.jpg
+18/05/26: La carta es publicada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a published menu
+2.  Copy the url
+3. Open the url in a navegator
+</t>
+  </si>
+  <si>
+    <r>
+      <t>1. A copy of the menu is c</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>eated</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">1. The user selects a menu and clicks the copy icon
+</t>
+  </si>
+  <si>
     <t>1. The user selects a menu and clicks the icon "+"
 2. Clicks "Despublicar"
-3. Clicks "Cancelar"</t>
-  </si>
-  <si>
-    <t>1. The menu is unpublished</t>
+3. Clicks "Cerrar"</t>
+  </si>
+  <si>
+    <t>Published menu: Delete</t>
+  </si>
+  <si>
+    <t>1. The user selects a menu published and clicks the garbage icon
+2. Clicks "Aceptar"</t>
+  </si>
+  <si>
+    <t>1. The Published menu is deleted.</t>
+  </si>
+  <si>
+    <t>Published menu: Delete,cancel</t>
+  </si>
+  <si>
+    <t>1. The user selects a menu published and clicks the garbage icon
+2. Clicks "Cancelar"</t>
+  </si>
+  <si>
+    <t>CAR014</t>
+  </si>
+  <si>
+    <t>CAR015</t>
+  </si>
+  <si>
+    <t>CAR016</t>
+  </si>
+  <si>
+    <t>CAR017</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,6 +384,19 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -371,7 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -403,12 +483,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -420,23 +503,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6565"/>
         </patternFill>
       </fill>
     </dxf>
@@ -774,7 +840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="6"/>
@@ -858,7 +924,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -884,15 +950,15 @@
         <v>13</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="9" t="s">
         <v>25</v>
@@ -904,7 +970,7 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>12</v>
@@ -913,10 +979,10 @@
     </row>
     <row r="6" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C6" s="9" t="s">
         <v>34</v>
@@ -937,10 +1003,10 @@
     </row>
     <row r="7" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C7" s="9" t="s">
         <v>33</v>
@@ -963,10 +1029,10 @@
     </row>
     <row r="8" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C8" s="9" t="s">
         <v>36</v>
@@ -989,10 +1055,10 @@
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C9" s="9" t="s">
         <v>41</v>
@@ -1011,98 +1077,98 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row r="10" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" s="3" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="3" customFormat="1" ht="105" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H11" s="10"/>
     </row>
-    <row r="12" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" s="3" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>58</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="F12" s="1"/>
       <c r="G12" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
       <c r="B13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>12</v>
@@ -1111,22 +1177,22 @@
     </row>
     <row r="14" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>12</v>
@@ -1135,60 +1201,124 @@
     </row>
     <row r="15" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H15" s="10"/>
     </row>
+    <row r="16" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="H18" s="10"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="G2:G3">
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="KO">
+  <conditionalFormatting sqref="G2:G18">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="KO">
       <formula>NOT(ISERROR(SEARCH("KO",G2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="OK">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="OK">
       <formula>NOT(ISERROR(SEARCH("OK",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G3">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="PTE">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G3)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="2" operator="containsText" text="BL">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G3)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G4:G15">
-    <cfRule type="containsText" dxfId="3" priority="7" operator="containsText" text="KO">
-      <formula>NOT(ISERROR(SEARCH("KO",G4)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="9" operator="containsText" text="OK">
-      <formula>NOT(ISERROR(SEARCH("OK",G4)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G8:G15">
+  <conditionalFormatting sqref="G8:G18">
     <cfRule type="containsText" dxfId="1" priority="6" operator="containsText" text="BL">
       <formula>NOT(ISERROR(SEARCH("BL",G8)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G9:G15">
+  <conditionalFormatting sqref="G9:G18">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="PTE">
       <formula>NOT(ISERROR(SEARCH("PTE",G9)))</formula>
     </cfRule>

--- a/Web/TestCasesWeb/Cartas.xlsx
+++ b/Web/TestCasesWeb/Cartas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nerea QA\PycharmProjects\KOVAI\Web\TestCasesWeb\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC15573F-AAA4-4B78-8431-42DE32B8969B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF4DF05-AD06-446F-B817-94F7A51474BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="81">
   <si>
     <t>Num</t>
   </si>
@@ -99,25 +99,7 @@
     <t>1. The menu is scanned.</t>
   </si>
   <si>
-    <t>1. The menu is not scanned.</t>
-  </si>
-  <si>
-    <t>Scan menu</t>
-  </si>
-  <si>
-    <t>Error: Scan menu</t>
-  </si>
-  <si>
-    <t>Add menu</t>
-  </si>
-  <si>
-    <t>Menus' home</t>
-  </si>
-  <si>
     <t>1. A modifier is created</t>
-  </si>
-  <si>
-    <t>1. A modifier is not created</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks "Modificadores"
@@ -132,16 +114,7 @@
     <t>https://drive.google.com/file/d/1iQVw2ssQU4ip7j2sEqfApVI-YwxE2qzW/view?usp=drive_link</t>
   </si>
   <si>
-    <t>New modifiers</t>
-  </si>
-  <si>
-    <t>Error: New menu, mandatory fields</t>
-  </si>
-  <si>
     <t>CAR006</t>
-  </si>
-  <si>
-    <t>Error: New modifier, mandatory fields</t>
   </si>
   <si>
     <t xml:space="preserve">1. The user clicks "Modificadores"
@@ -159,9 +132,6 @@
     <t>CAR007</t>
   </si>
   <si>
-    <t>Select diferents restaurants</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. The user clicks a "Restaurante"
 </t>
   </si>
@@ -173,9 +143,6 @@
   </si>
   <si>
     <t>1. The menu is published</t>
-  </si>
-  <si>
-    <t>Published menu</t>
   </si>
   <si>
     <t>15/04/26 : Error: carta_sca.jpg</t>
@@ -200,16 +167,7 @@
     </r>
   </si>
   <si>
-    <t>Published menu: QR</t>
-  </si>
-  <si>
-    <t>Published menu: Unpublish</t>
-  </si>
-  <si>
     <t>1. The QR works correctly.</t>
-  </si>
-  <si>
-    <t>Published menu: Unpublish, cancel</t>
   </si>
   <si>
     <t>CAR009</t>
@@ -235,12 +193,6 @@
     <t>1. The menu is unpublished</t>
   </si>
   <si>
-    <t>Published menu: Copy</t>
-  </si>
-  <si>
-    <t>Published menu: cancel</t>
-  </si>
-  <si>
     <t>1. The user selects a menu and clicks the icon "+"
 2. The message "Publicar esta carta la hará accesible mediante un enlace público y un código QR que los clientes pueden escanear desde sus dispositivos móviles." is shown
 3. Clicks "Publicar carta"</t>
@@ -254,9 +206,6 @@
     <t xml:space="preserve">1. The user selects a published menu
 2.  Scans the QR
 </t>
-  </si>
-  <si>
-    <t>Published menu: URL</t>
   </si>
   <si>
     <t xml:space="preserve">1. QR works correctly.
@@ -314,9 +263,6 @@
 3. Clicks "Cerrar"</t>
   </si>
   <si>
-    <t>Published menu: Delete</t>
-  </si>
-  <si>
     <t>1. The user selects a menu published and clicks the garbage icon
 2. Clicks "Aceptar"</t>
   </si>
@@ -324,9 +270,6 @@
     <t>1. The Published menu is deleted.</t>
   </si>
   <si>
-    <t>Published menu: Delete,cancel</t>
-  </si>
-  <si>
     <t>1. The user selects a menu published and clicks the garbage icon
 2. Clicks "Cancelar"</t>
   </si>
@@ -341,6 +284,57 @@
   </si>
   <si>
     <t>CAR017</t>
+  </si>
+  <si>
+    <t>Menus home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menus: Add </t>
+  </si>
+  <si>
+    <t>Menus: Scan</t>
+  </si>
+  <si>
+    <t>Menus: Error Scan</t>
+  </si>
+  <si>
+    <t>Menus: add mandatory fields, error</t>
+  </si>
+  <si>
+    <t>Menus: New modifiers</t>
+  </si>
+  <si>
+    <t>Menus: New modifier, mandatory fields, error</t>
+  </si>
+  <si>
+    <t>Menus: Select diferents restaurants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Menus: Published </t>
+  </si>
+  <si>
+    <t>Menus: Published, cancel</t>
+  </si>
+  <si>
+    <t>Menus: Published, URL</t>
+  </si>
+  <si>
+    <t>Menus: Published, QR</t>
+  </si>
+  <si>
+    <t>Menus: Published, Copy</t>
+  </si>
+  <si>
+    <t>Menus: Unpublish, cancel</t>
+  </si>
+  <si>
+    <t>Menus:  Unpublish</t>
+  </si>
+  <si>
+    <t>Menus: Published, Delete</t>
+  </si>
+  <si>
+    <t>Menus: Published Delete,cancel</t>
   </si>
 </sst>
 </file>
@@ -887,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>20</v>
@@ -911,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>18</v>
@@ -924,7 +918,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -935,7 +929,7 @@
         <v>10</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
@@ -943,14 +937,12 @@
       <c r="E4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="F4" s="1"/>
       <c r="G4" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="3" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -961,7 +953,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -982,13 +974,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>17</v>
@@ -1006,25 +998,23 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>29</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F7" s="1"/>
       <c r="G7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1032,13 +1022,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>17</v>
@@ -1047,10 +1037,10 @@
         <v>17</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="3" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -1058,19 +1048,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>12</v>
@@ -1082,25 +1072,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="3" customFormat="1" ht="105" x14ac:dyDescent="0.25">
@@ -1108,13 +1098,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>16</v>
@@ -1132,23 +1122,23 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="3" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -1156,19 +1146,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>12</v>
@@ -1180,19 +1170,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>12</v>
@@ -1204,19 +1194,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>12</v>
@@ -1228,13 +1218,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>16</v>
@@ -1252,19 +1242,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>12</v>
@@ -1276,13 +1266,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>16</v>
